--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3511071647</v>
+        <v>179970919</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>3866428</v>
+        <v>61175</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.1297</v>
+        <v>0.0399</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.1072</v>
+        <v>0.0224</v>
       </c>
     </row>
   </sheetData>

--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/투자수익현황_2026-08-21_2026-08-27.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>61175</v>
+        <v>198184</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.0399</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.0319</v>
+        <v>0.1034</v>
       </c>
     </row>
   </sheetData>
